--- a/src/sources/exercises.xlsx
+++ b/src/sources/exercises.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Илья\Documents\physics\src\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F944CF-F223-4A83-9C2D-7BBEE646D3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BEA24E-81EE-425F-BA7C-D308753A330B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
   </bookViews>
@@ -26,12 +26,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6404" uniqueCount="3244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6404" uniqueCount="3248">
   <si>
     <r>
       <t xml:space="preserve">Множество </t>
@@ -9815,10 +9818,22 @@
     <t>Стоимость прямо пропорциональна массе. Найдите цену за 1 кг.</t>
   </si>
   <si>
-    <t>Просто введи ответ: 6</t>
-  </si>
-  <si>
     <t>Какова длина диагонали прямоугольника со сторонами 3 и 4?</t>
+  </si>
+  <si>
+    <t>Если высоту столба сделать в 10 раз больше, во сколько раз увеличится длина его тени?</t>
+  </si>
+  <si>
+    <t>Исходя из рисунка, сколько капель упадёт через 4 секунды?</t>
+  </si>
+  <si>
+    <t>Исходя из рисунка, какова будет длина тени, если высоту столба сделать 6 метров?</t>
+  </si>
+  <si>
+    <t>Исходя из рисунка, через сколько секунд упадет только одна капля?</t>
+  </si>
+  <si>
+    <t>Исходя из рисунка, через сколько часов завод сделает 6 деталей?</t>
   </si>
 </sst>
 </file>
@@ -12409,7 +12424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="15.6">
+    <row r="81" spans="1:6" ht="28.8">
       <c r="A81" s="8">
         <v>4</v>
       </c>
@@ -12423,13 +12438,13 @@
         <v>135</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>3242</v>
+        <v>3243</v>
       </c>
       <c r="F81" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="15.6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="28.8">
       <c r="A82" s="8">
         <v>4</v>
       </c>
@@ -12443,13 +12458,13 @@
         <v>136</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>104</v>
+        <v>3244</v>
       </c>
       <c r="F82" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="15.6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="28.8">
       <c r="A83" s="8">
         <v>4</v>
       </c>
@@ -12463,13 +12478,13 @@
         <v>137</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>104</v>
+        <v>3245</v>
       </c>
       <c r="F83" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="15.6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="28.8">
       <c r="A84" s="8">
         <v>4</v>
       </c>
@@ -12483,13 +12498,13 @@
         <v>138</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>104</v>
+        <v>3246</v>
       </c>
       <c r="F84" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="15.6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="28.8">
       <c r="A85" s="8">
         <v>4</v>
       </c>
@@ -12503,10 +12518,10 @@
         <v>139</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>104</v>
+        <v>3247</v>
       </c>
       <c r="F85" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="15.6">
@@ -17223,7 +17238,7 @@
         <v>375</v>
       </c>
       <c r="E321" s="10" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="F321" s="8">
         <v>5</v>

--- a/src/sources/exercises.xlsx
+++ b/src/sources/exercises.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Илья\Documents\physics\src\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF262381-B984-497B-B3C8-C4F38AA24684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DA2120-5F58-454A-839C-F57218A04DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12912" yWindow="3276" windowWidth="17280" windowHeight="9780" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
+    <workbookView xWindow="5760" yWindow="2580" windowWidth="17280" windowHeight="9780" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
@@ -9770,9 +9770,6 @@
     <t>Прямая пропорциональность — когда обе величины изменяются одинаково (увеличиваются/уменьшаются в одинаковое число раз).</t>
   </si>
   <si>
-    <t>Найдите стоимость 1 кг (360 ÷ 3 = 120), затем умножьте на 7.</t>
-  </si>
-  <si>
     <t>Если нужно сшить в 2 раза больше платьев, ткани потребуется в 2 раза больше.</t>
   </si>
   <si>
@@ -9909,6 +9906,9 @@
   </si>
   <si>
     <t>А ты поддумай или наддумай? Мб ответ в метрах.</t>
+  </si>
+  <si>
+    <t>Найдите стоимость 1 кг (360 ÷ 3 = 120), затем умножьте на 7</t>
   </si>
 </sst>
 </file>
@@ -11190,7 +11190,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>13</v>
@@ -12493,7 +12493,7 @@
         <v>133</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="F80" s="8">
         <v>10</v>
@@ -12513,7 +12513,7 @@
         <v>134</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="F81" s="8">
         <v>8</v>
@@ -12533,7 +12533,7 @@
         <v>135</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="F82" s="8">
         <v>9</v>
@@ -12553,7 +12553,7 @@
         <v>136</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F83" s="8">
         <v>0.5</v>
@@ -12573,7 +12573,7 @@
         <v>137</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="F84" s="8">
         <v>3</v>
@@ -12779,7 +12779,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="43.2">
+    <row r="95" spans="1:6" ht="57.6">
       <c r="A95" s="8">
         <v>4</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>149</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>3226</v>
+        <v>3272</v>
       </c>
       <c r="F96" s="8">
         <v>840</v>
@@ -12833,7 +12833,7 @@
         <v>150</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="F97" s="8">
         <v>112</v>
@@ -12853,7 +12853,7 @@
         <v>151</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="F98" s="8">
         <v>15</v>
@@ -12873,7 +12873,7 @@
         <v>152</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="F99" s="8">
         <v>12</v>
@@ -12893,7 +12893,7 @@
         <v>153</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="F100" s="8">
         <v>6000</v>
@@ -12913,7 +12913,7 @@
         <v>154</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="F101" s="8">
         <v>12</v>
@@ -12933,7 +12933,7 @@
         <v>155</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="F102" s="8">
         <v>2</v>
@@ -12953,7 +12953,7 @@
         <v>156</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="F103" s="8">
         <v>1500</v>
@@ -12973,7 +12973,7 @@
         <v>157</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="F104" s="8">
         <v>112</v>
@@ -12993,7 +12993,7 @@
         <v>158</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="F105" s="8">
         <v>6</v>
@@ -13013,7 +13013,7 @@
         <v>159</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="F106" s="8">
         <v>12</v>
@@ -13033,7 +13033,7 @@
         <v>160</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="F107" s="8">
         <v>12</v>
@@ -13053,7 +13053,7 @@
         <v>161</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="F108" s="8">
         <v>800</v>
@@ -13073,7 +13073,7 @@
         <v>162</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="F109" s="8">
         <v>560</v>
@@ -17293,7 +17293,7 @@
         <v>373</v>
       </c>
       <c r="E320" s="10" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="F320" s="8">
         <v>5</v>
@@ -17313,7 +17313,7 @@
         <v>374</v>
       </c>
       <c r="E321" s="10" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="F321" s="8">
         <v>2</v>
@@ -17333,13 +17333,13 @@
         <v>375</v>
       </c>
       <c r="E322" s="10" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="F322" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:6" ht="15.6">
+    <row r="323" spans="1:6" ht="28.8">
       <c r="A323" s="8">
         <v>12</v>
       </c>
@@ -17353,7 +17353,7 @@
         <v>376</v>
       </c>
       <c r="E323" s="10" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="F323" s="8">
         <v>0.57699999999999996</v>
@@ -17373,7 +17373,7 @@
         <v>377</v>
       </c>
       <c r="E324" s="10" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="F324" s="8">
         <v>1</v>
@@ -17393,7 +17393,7 @@
         <v>378</v>
       </c>
       <c r="E325" s="10" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="F325" s="8">
         <v>0.7</v>
@@ -17413,13 +17413,13 @@
         <v>379</v>
       </c>
       <c r="E326" s="10" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="F326" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:6" ht="15.6">
+    <row r="327" spans="1:6" ht="28.8">
       <c r="A327" s="8">
         <v>12</v>
       </c>
@@ -17433,7 +17433,7 @@
         <v>380</v>
       </c>
       <c r="E327" s="10" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="F327" s="8">
         <v>0.86599999999999999</v>
@@ -17453,7 +17453,7 @@
         <v>381</v>
       </c>
       <c r="E328" s="10" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="F328" s="8">
         <v>6</v>
@@ -17473,7 +17473,7 @@
         <v>382</v>
       </c>
       <c r="E329" s="10" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="F329" s="8">
         <v>2</v>
@@ -17493,7 +17493,7 @@
         <v>383</v>
       </c>
       <c r="E330" s="10" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="F330" s="8">
         <v>13</v>
@@ -17513,7 +17513,7 @@
         <v>384</v>
       </c>
       <c r="E331" s="10" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="F331" s="8">
         <v>0.5</v>
@@ -17533,7 +17533,7 @@
         <v>385</v>
       </c>
       <c r="E332" s="10" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="F332" s="8">
         <v>1</v>
@@ -17553,10 +17553,10 @@
         <v>386</v>
       </c>
       <c r="E333" s="10" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="F333" s="8" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="334" spans="1:6" ht="28.8">
@@ -17573,7 +17573,7 @@
         <v>387</v>
       </c>
       <c r="E334" s="10" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="F334" s="8">
         <v>4</v>
@@ -17593,7 +17593,7 @@
         <v>388</v>
       </c>
       <c r="E335" s="10" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="F335" s="8">
         <v>13</v>
@@ -17613,7 +17613,7 @@
         <v>389</v>
       </c>
       <c r="E336" s="10" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="F336" s="8">
         <v>5</v>
@@ -17633,10 +17633,10 @@
         <v>390</v>
       </c>
       <c r="E337" s="10" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="F337" s="8" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="338" spans="1:6" ht="43.2">
@@ -17653,7 +17653,7 @@
         <v>391</v>
       </c>
       <c r="E338" s="10" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="F338" s="8">
         <v>2</v>
@@ -17673,7 +17673,7 @@
         <v>392</v>
       </c>
       <c r="E339" s="10" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="F339" s="8">
         <v>0.28000000000000003</v>
@@ -17693,7 +17693,7 @@
         <v>393</v>
       </c>
       <c r="E340" s="10" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="F340" s="8">
         <v>45</v>
@@ -17713,7 +17713,7 @@
         <v>394</v>
       </c>
       <c r="E341" s="10" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="F341" s="8">
         <v>123</v>
@@ -17733,7 +17733,7 @@
         <v>395</v>
       </c>
       <c r="E342" s="10" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="F342" s="8">
         <v>10</v>
@@ -17753,7 +17753,7 @@
         <v>396</v>
       </c>
       <c r="E343" s="10" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="F343" s="8">
         <v>1</v>
@@ -17773,7 +17773,7 @@
         <v>397</v>
       </c>
       <c r="E344" s="10" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="F344" s="8">
         <v>13</v>
@@ -17793,7 +17793,7 @@
         <v>398</v>
       </c>
       <c r="E345" s="10" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="F345" s="8">
         <v>6</v>
@@ -17813,7 +17813,7 @@
         <v>399</v>
       </c>
       <c r="E346" s="10" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="F346" s="8">
         <v>80</v>
@@ -17833,7 +17833,7 @@
         <v>400</v>
       </c>
       <c r="E347" s="10" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="F347" s="8">
         <v>4</v>

--- a/src/sources/exercises.xlsx
+++ b/src/sources/exercises.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Илья\Documents\physics\src\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DA2120-5F58-454A-839C-F57218A04DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8939AD7-09FD-4CBD-81C4-16505EE39781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="2580" windowWidth="17280" windowHeight="9780" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
+    <workbookView xWindow="13332" yWindow="2880" windowWidth="17280" windowHeight="9780" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
@@ -9821,9 +9821,6 @@
     <t>Исходя из рисунка, через сколько часов завод сделает 6 деталей?</t>
   </si>
   <si>
-    <t>Вспомни теорему Пифагора</t>
-  </si>
-  <si>
     <t>Img.1.1.2.5</t>
   </si>
   <si>
@@ -9833,30 +9830,18 @@
     <t>Если катеты равны, чему равен тангенс соответствующего угла?</t>
   </si>
   <si>
-    <t>Чему равен синус 45 градусов (согласно таблице)?</t>
-  </si>
-  <si>
     <t>Если противолежавший катет равен гипотенузе, чему равен синус угла альфа (согласно рисунку)?</t>
   </si>
   <si>
-    <t>Чему равен тангенс 30 градусов (согласно таблице)?</t>
-  </si>
-  <si>
     <t>Если прилежащий катет равен гипотенузе, чему равен косинус угла альфа (согласно рисунку)?</t>
   </si>
   <si>
-    <t>Чему равен косинус 30 градусов (согласно таблице)?</t>
-  </si>
-  <si>
     <t>Обрати внимание на первое слово утверждения</t>
   </si>
   <si>
     <t xml:space="preserve">Сумма острых углов прямоугольного треугольника всегда равна 90 </t>
   </si>
   <si>
-    <t xml:space="preserve">Косинус 60 градусов равен синуса 30 градусов </t>
-  </si>
-  <si>
     <t xml:space="preserve">Угол указан в радианах </t>
   </si>
   <si>
@@ -9878,12 +9863,6 @@
     <t xml:space="preserve">Представьте синус и косинус, как отношении соответствующих сторон к гипотенузе, и поделите одно, на другое. Ответ напиши с большой буквы. </t>
   </si>
   <si>
-    <t>Представь, ЧТО образуют все три силы (горизонтальная, вертикальная, направленная под углом α) вместе.</t>
-  </si>
-  <si>
-    <t>Для начала найди гипотенузу</t>
-  </si>
-  <si>
     <t>Ответ содержит от 1 до 3 утверждений</t>
   </si>
   <si>
@@ -9909,6 +9888,27 @@
   </si>
   <si>
     <t>Найдите стоимость 1 кг (360 ÷ 3 = 120), затем умножьте на 7</t>
+  </si>
+  <si>
+    <t>Чему равен тангенс 30 градусов (согласно таблице)? Используйте точку вместо запятой.</t>
+  </si>
+  <si>
+    <t>Чему равен синус 45 градусов (согласно таблице)? Используйте точку вместо запятой.</t>
+  </si>
+  <si>
+    <t>Чему равен косинус 30 градусов (согласно таблице)? Используйте точку вместо запятой.</t>
+  </si>
+  <si>
+    <t>Вспомни теорему Пифагора. Дайте ответ в сантиметрах.</t>
+  </si>
+  <si>
+    <t>Косинус 60 градусов равен синуса 30 градусов. Используйте точку вместо запятой.</t>
+  </si>
+  <si>
+    <t>Для начала найди гипотенузу. Используйте точку вместо запятой.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Угол 30 градусов.</t>
   </si>
 </sst>
 </file>
@@ -11190,7 +11190,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>13</v>
@@ -12813,7 +12813,7 @@
         <v>149</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>3272</v>
+        <v>3265</v>
       </c>
       <c r="F96" s="8">
         <v>840</v>
@@ -17313,7 +17313,7 @@
         <v>374</v>
       </c>
       <c r="E321" s="10" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="F321" s="8">
         <v>2</v>
@@ -17333,7 +17333,7 @@
         <v>375</v>
       </c>
       <c r="E322" s="10" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="F322" s="8">
         <v>1</v>
@@ -17353,7 +17353,7 @@
         <v>376</v>
       </c>
       <c r="E323" s="10" t="s">
-        <v>3249</v>
+        <v>3266</v>
       </c>
       <c r="F323" s="8">
         <v>0.57699999999999996</v>
@@ -17373,13 +17373,13 @@
         <v>377</v>
       </c>
       <c r="E324" s="10" t="s">
-        <v>3248</v>
+        <v>3246</v>
       </c>
       <c r="F324" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:6" ht="15.6">
+    <row r="325" spans="1:6" ht="28.8">
       <c r="A325" s="8">
         <v>12</v>
       </c>
@@ -17393,7 +17393,7 @@
         <v>378</v>
       </c>
       <c r="E325" s="10" t="s">
-        <v>3247</v>
+        <v>3267</v>
       </c>
       <c r="F325" s="8">
         <v>0.7</v>
@@ -17413,7 +17413,7 @@
         <v>379</v>
       </c>
       <c r="E326" s="10" t="s">
-        <v>3250</v>
+        <v>3247</v>
       </c>
       <c r="F326" s="8">
         <v>1</v>
@@ -17433,13 +17433,13 @@
         <v>380</v>
       </c>
       <c r="E327" s="10" t="s">
-        <v>3251</v>
+        <v>3268</v>
       </c>
       <c r="F327" s="8">
         <v>0.86599999999999999</v>
       </c>
     </row>
-    <row r="328" spans="1:6" ht="15.6">
+    <row r="328" spans="1:6" ht="28.8">
       <c r="A328" s="8">
         <v>12</v>
       </c>
@@ -17453,7 +17453,7 @@
         <v>381</v>
       </c>
       <c r="E328" s="10" t="s">
-        <v>3243</v>
+        <v>3269</v>
       </c>
       <c r="F328" s="8">
         <v>6</v>
@@ -17473,7 +17473,7 @@
         <v>382</v>
       </c>
       <c r="E329" s="10" t="s">
-        <v>3252</v>
+        <v>3248</v>
       </c>
       <c r="F329" s="8">
         <v>2</v>
@@ -17493,13 +17493,13 @@
         <v>383</v>
       </c>
       <c r="E330" s="10" t="s">
-        <v>3253</v>
+        <v>3249</v>
       </c>
       <c r="F330" s="8">
         <v>13</v>
       </c>
     </row>
-    <row r="331" spans="1:6" ht="15.6">
+    <row r="331" spans="1:6" ht="28.8">
       <c r="A331" s="8">
         <v>12</v>
       </c>
@@ -17513,7 +17513,7 @@
         <v>384</v>
       </c>
       <c r="E331" s="10" t="s">
-        <v>3254</v>
+        <v>3270</v>
       </c>
       <c r="F331" s="8">
         <v>0.5</v>
@@ -17533,7 +17533,7 @@
         <v>385</v>
       </c>
       <c r="E332" s="10" t="s">
-        <v>3255</v>
+        <v>3250</v>
       </c>
       <c r="F332" s="8">
         <v>1</v>
@@ -17553,10 +17553,10 @@
         <v>386</v>
       </c>
       <c r="E333" s="10" t="s">
-        <v>3257</v>
+        <v>3252</v>
       </c>
       <c r="F333" s="8" t="s">
-        <v>3256</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="334" spans="1:6" ht="28.8">
@@ -17573,7 +17573,7 @@
         <v>387</v>
       </c>
       <c r="E334" s="10" t="s">
-        <v>3258</v>
+        <v>3253</v>
       </c>
       <c r="F334" s="8">
         <v>4</v>
@@ -17593,7 +17593,7 @@
         <v>388</v>
       </c>
       <c r="E335" s="10" t="s">
-        <v>3259</v>
+        <v>3254</v>
       </c>
       <c r="F335" s="8">
         <v>13</v>
@@ -17613,7 +17613,7 @@
         <v>389</v>
       </c>
       <c r="E336" s="10" t="s">
-        <v>3260</v>
+        <v>3255</v>
       </c>
       <c r="F336" s="8">
         <v>5</v>
@@ -17633,13 +17633,13 @@
         <v>390</v>
       </c>
       <c r="E337" s="10" t="s">
-        <v>3261</v>
+        <v>3256</v>
       </c>
       <c r="F337" s="8" t="s">
-        <v>3256</v>
-      </c>
-    </row>
-    <row r="338" spans="1:6" ht="43.2">
+        <v>3251</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" ht="15.6">
       <c r="A338" s="8">
         <v>12</v>
       </c>
@@ -17653,13 +17653,13 @@
         <v>391</v>
       </c>
       <c r="E338" s="10" t="s">
-        <v>3262</v>
+        <v>3272</v>
       </c>
       <c r="F338" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="339" spans="1:6" ht="15.6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" ht="28.8">
       <c r="A339" s="8">
         <v>12</v>
       </c>
@@ -17673,7 +17673,7 @@
         <v>392</v>
       </c>
       <c r="E339" s="10" t="s">
-        <v>3263</v>
+        <v>3271</v>
       </c>
       <c r="F339" s="8">
         <v>0.28000000000000003</v>
@@ -17693,7 +17693,7 @@
         <v>393</v>
       </c>
       <c r="E340" s="10" t="s">
-        <v>3270</v>
+        <v>3263</v>
       </c>
       <c r="F340" s="8">
         <v>45</v>
@@ -17713,7 +17713,7 @@
         <v>394</v>
       </c>
       <c r="E341" s="10" t="s">
-        <v>3264</v>
+        <v>3257</v>
       </c>
       <c r="F341" s="8">
         <v>123</v>
@@ -17733,7 +17733,7 @@
         <v>395</v>
       </c>
       <c r="E342" s="10" t="s">
-        <v>3265</v>
+        <v>3258</v>
       </c>
       <c r="F342" s="8">
         <v>10</v>
@@ -17753,7 +17753,7 @@
         <v>396</v>
       </c>
       <c r="E343" s="10" t="s">
-        <v>3266</v>
+        <v>3259</v>
       </c>
       <c r="F343" s="8">
         <v>1</v>
@@ -17773,7 +17773,7 @@
         <v>397</v>
       </c>
       <c r="E344" s="10" t="s">
-        <v>3267</v>
+        <v>3260</v>
       </c>
       <c r="F344" s="8">
         <v>13</v>
@@ -17793,7 +17793,7 @@
         <v>398</v>
       </c>
       <c r="E345" s="10" t="s">
-        <v>3268</v>
+        <v>3261</v>
       </c>
       <c r="F345" s="8">
         <v>6</v>
@@ -17813,7 +17813,7 @@
         <v>399</v>
       </c>
       <c r="E346" s="10" t="s">
-        <v>3271</v>
+        <v>3264</v>
       </c>
       <c r="F346" s="8">
         <v>80</v>
@@ -17833,7 +17833,7 @@
         <v>400</v>
       </c>
       <c r="E347" s="10" t="s">
-        <v>3269</v>
+        <v>3262</v>
       </c>
       <c r="F347" s="8">
         <v>4</v>

--- a/src/sources/exercises.xlsx
+++ b/src/sources/exercises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Илья\Documents\physics\src\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75DCD81-8A3A-472B-837A-53DFD936A1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2F0A6D-4909-43BB-A725-A3AB6235AF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6425" uniqueCount="3305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6424" uniqueCount="3305">
   <si>
     <r>
       <t xml:space="preserve">Множество </t>
@@ -21640,8 +21640,8 @@
       <c r="E530" s="10" t="s">
         <v>3274</v>
       </c>
-      <c r="F530" s="8" t="s">
-        <v>3275</v>
+      <c r="F530" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="531" spans="1:6" ht="28.8">

--- a/src/sources/exercises.xlsx
+++ b/src/sources/exercises.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Илья\Documents\physics\src\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C119BA-B68D-479C-8D1A-F771B862CAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97586A1E-D43E-4131-A1CA-7B431C56F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22992" windowHeight="7188" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>

--- a/src/sources/exercises.xlsx
+++ b/src/sources/exercises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Илья\Documents\physics\src\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97586A1E-D43E-4131-A1CA-7B431C56F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C307C57-09B5-4DC9-915B-A618120690ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
   </bookViews>

--- a/src/sources/exercises.xlsx
+++ b/src/sources/exercises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Илья\Documents\physics\src\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C307C57-09B5-4DC9-915B-A618120690ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCDFC17-B90F-4D74-B61A-0D9B2ADF8F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
   </bookViews>
@@ -55987,9 +55987,15 @@
       </c>
     </row>
     <row r="2244" spans="1:6" ht="15.6">
-      <c r="A2244" s="8"/>
-      <c r="B2244" s="8"/>
-      <c r="C2244" s="8"/>
+      <c r="A2244" s="8">
+        <v>76</v>
+      </c>
+      <c r="B2244" s="8">
+        <v>1</v>
+      </c>
+      <c r="C2244" s="8">
+        <v>11</v>
+      </c>
       <c r="D2244" s="13" t="s">
         <v>3323</v>
       </c>

--- a/src/sources/exercises.xlsx
+++ b/src/sources/exercises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Илья\Documents\physics\src\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DEC5F1-CE37-4AC3-9247-BF48AAAD2C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F9765F-AA80-49D9-8ACF-E3D7744891B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
   </bookViews>
@@ -10178,10 +10178,10 @@
     <t>Сопротивление прямо пропорционально длине и обратно пропорционально площади. Чтобы сопротивление не изменилось при увеличении длины, нужно увеличить площадь во столько же раз, во сколько выросла длина. Посчитай, во сколько раз увеличилась длина кабеля.</t>
   </si>
   <si>
-    <t>Не забудь перевести длину из сантиметров в метры, так как удельное сопротивление дано для длины в 1 метр. Затем подставь значения в формулу: удельное сопротивление меди умножь на длину в метрах и раздели на площадь сечения</t>
-  </si>
-  <si>
     <t>Чтобы найти длину, нужно сначала определить сопротивление проводника. Для этого выбери любую точку на графике и раздели напряжение на силу тока. Затем, зная удельное сопротивление никелина (0,4) и площадь сечения (0,8), вырази длину из формулы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Не забудь перевести длину из сантиметров в метры, используйте точку вместо запятой при записи дробной части </t>
   </si>
 </sst>
 </file>
@@ -59200,7 +59200,7 @@
         <v>3338</v>
       </c>
       <c r="E2400" t="s">
-        <v>3343</v>
+        <v>3344</v>
       </c>
       <c r="F2400">
         <v>3.3999999999999998E-3</v>
@@ -59220,7 +59220,7 @@
         <v>3339</v>
       </c>
       <c r="E2401" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="F2401" s="8">
         <v>10</v>

--- a/src/sources/exercises.xlsx
+++ b/src/sources/exercises.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Илья\Documents\physics\src\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FBD5F4-8616-4AEF-8196-E8619C893199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18386C11-804B-48BF-AA8C-1A0819E58949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7464" yWindow="2892" windowWidth="22992" windowHeight="7188" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6444" uniqueCount="3368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6443" uniqueCount="3367">
   <si>
     <r>
       <t xml:space="preserve">Множество </t>
@@ -10206,9 +10206,6 @@
   </si>
   <si>
     <t>Надо силу тяжести раздели на площадь основания фигуры (используйте точку вместо запятой)</t>
-  </si>
-  <si>
-    <t>0.156</t>
   </si>
   <si>
     <r>
@@ -40512,8 +40509,8 @@
       <c r="E1461" s="18" t="s">
         <v>3352</v>
       </c>
-      <c r="F1461" s="18" t="s">
-        <v>3353</v>
+      <c r="F1461" s="18">
+        <v>1560</v>
       </c>
     </row>
     <row r="1462" spans="1:6" ht="15.6">
@@ -40530,7 +40527,7 @@
         <v>1513</v>
       </c>
       <c r="E1462" s="18" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="F1462">
         <v>6240</v>
@@ -40550,7 +40547,7 @@
         <v>1514</v>
       </c>
       <c r="E1463" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="F1463" s="18">
         <v>20000</v>
@@ -40567,10 +40564,10 @@
         <v>11</v>
       </c>
       <c r="D1464" s="13" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="E1464" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="F1464" s="8">
         <v>20000</v>
@@ -40587,10 +40584,10 @@
         <v>12</v>
       </c>
       <c r="D1465" s="13" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="E1465" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="F1465">
         <v>100000</v>
@@ -40607,10 +40604,10 @@
         <v>13</v>
       </c>
       <c r="D1466" s="13" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="E1466" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="F1466">
         <v>112270000</v>
@@ -40627,10 +40624,10 @@
         <v>14</v>
       </c>
       <c r="D1467" s="13" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="E1467" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="F1467">
         <v>20000</v>
@@ -40647,10 +40644,10 @@
         <v>15</v>
       </c>
       <c r="D1468" s="13" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="E1468" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="F1468" s="18">
         <v>2</v>
@@ -40667,10 +40664,10 @@
         <v>16</v>
       </c>
       <c r="D1469" s="13" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="E1469" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="F1469" s="18">
         <v>10</v>

--- a/src/sources/exercises.xlsx
+++ b/src/sources/exercises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Илья\Documents\physics\src\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E52FD93-82D3-4114-AD39-6F81C93CDFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247AE760-5586-40DD-BB28-9C07B50631B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6457" uniqueCount="3391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6457" uniqueCount="3399">
   <si>
     <r>
       <t xml:space="preserve">Множество </t>
@@ -10287,9 +10287,6 @@
     <t>На сколько градусов поворачивается вектор R за одну секунду?</t>
   </si>
   <si>
-    <t>Угол в радианах показывает во сколько раз длина дуги больше чем радиус, соответственно, чтобы получить длину дуги надо угол в радианах умножить на радиус</t>
-  </si>
-  <si>
     <t>45 градусов - это 1 / 8 ццелого поворота</t>
   </si>
   <si>
@@ -10308,9 +10305,6 @@
     <t>Угловая частота - это линейная частота умноженная на 2 Пи</t>
   </si>
   <si>
-    <t>Косинус - это отношение прилежащего катета (тени) и гипотенузы (вектора дающего тень)</t>
-  </si>
-  <si>
     <t>Амплитуда - это длина нити, умноженная на косинус угла бетта</t>
   </si>
   <si>
@@ -10333,13 +10327,43 @@
   </si>
   <si>
     <t>Длина волны - это скорость волны, умноженная на период колебания точки</t>
+  </si>
+  <si>
+    <t>Угол в радианах показывает во сколько раз длина дуги больше чем радиус, соответственно, чтобы получить длину дуги надо угол в радианах умножить на радиус, ответ округли до десятых</t>
+  </si>
+  <si>
+    <t>Косинус - это отношение прилежащего катета (тени) и гипотенузы (вектора дающего тень), округлите до второого знака после запятой</t>
+  </si>
+  <si>
+    <t>Сила Архимеда равна весу вытесненной жидкости, вес 1 кг  = 10 Ньютонам</t>
+  </si>
+  <si>
+    <t>Сила Архимеда - это плотность жидкости (или газа), в которую погружено тело, умноженная на ускорение свободного падения, и на ускорение свободного падения</t>
+  </si>
+  <si>
+    <t>Внутри скобок осталась разность глубин, а это высота тела</t>
+  </si>
+  <si>
+    <t>Сала Архимеда -- это разность сил вверх и вниз, а сила - это давление, умноженное на площадь поверхности</t>
+  </si>
+  <si>
+    <t>Сила - это давление, умноженное на площадь поверхности</t>
+  </si>
+  <si>
+    <t>Сила Архимеда - это разность между силой, действующий снизу вверх, и силой действующей сверху вниз</t>
+  </si>
+  <si>
+    <t>Давление жидкости = плотность этой жидкости * ускорение свободного падения * глубина в метрах</t>
+  </si>
+  <si>
+    <t>Сила на каждую единицу площади действует одинаковое давление</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10594,6 +10618,14 @@
     </font>
     <font>
       <sz val="9.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -10957,7 +10989,7 @@
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -11015,6 +11047,7 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% — акцент1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -41761,11 +41794,11 @@
       <c r="D1520" s="13" t="s">
         <v>1565</v>
       </c>
-      <c r="E1520" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F1520" s="8">
-        <v>5</v>
+      <c r="E1520" t="s">
+        <v>3398</v>
+      </c>
+      <c r="F1520">
+        <v>50000</v>
       </c>
     </row>
     <row r="1521" spans="1:6" ht="15.6">
@@ -41781,11 +41814,11 @@
       <c r="D1521" s="13" t="s">
         <v>1566</v>
       </c>
-      <c r="E1521" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F1521" s="8">
-        <v>5</v>
+      <c r="E1521" t="s">
+        <v>3397</v>
+      </c>
+      <c r="F1521">
+        <v>50000</v>
       </c>
     </row>
     <row r="1522" spans="1:6" ht="15.6">
@@ -41801,11 +41834,11 @@
       <c r="D1522" s="13" t="s">
         <v>1567</v>
       </c>
-      <c r="E1522" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F1522" s="8">
-        <v>5</v>
+      <c r="E1522" t="s">
+        <v>3364</v>
+      </c>
+      <c r="F1522">
+        <v>10000</v>
       </c>
     </row>
     <row r="1523" spans="1:6" ht="15.6">
@@ -41821,11 +41854,11 @@
       <c r="D1523" s="13" t="s">
         <v>1568</v>
       </c>
-      <c r="E1523" s="10" t="s">
-        <v>101</v>
+      <c r="E1523" t="s">
+        <v>3396</v>
       </c>
       <c r="F1523" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1524" spans="1:6" ht="15.6">
@@ -41841,11 +41874,11 @@
       <c r="D1524" s="13" t="s">
         <v>1569</v>
       </c>
-      <c r="E1524" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F1524" s="8">
-        <v>5</v>
+      <c r="E1524" t="s">
+        <v>3395</v>
+      </c>
+      <c r="F1524">
+        <v>30000</v>
       </c>
     </row>
     <row r="1525" spans="1:6" ht="15.6">
@@ -41861,11 +41894,11 @@
       <c r="D1525" s="13" t="s">
         <v>1570</v>
       </c>
-      <c r="E1525" s="10" t="s">
-        <v>101</v>
+      <c r="E1525" t="s">
+        <v>3394</v>
       </c>
       <c r="F1525" s="8">
-        <v>5</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1526" spans="1:6" ht="15.6">
@@ -41881,11 +41914,11 @@
       <c r="D1526" s="13" t="s">
         <v>1571</v>
       </c>
-      <c r="E1526" s="10" t="s">
-        <v>101</v>
+      <c r="E1526" t="s">
+        <v>3394</v>
       </c>
       <c r="F1526" s="8">
-        <v>5</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1527" spans="1:6" ht="15.6">
@@ -41901,11 +41934,11 @@
       <c r="D1527" s="13" t="s">
         <v>1572</v>
       </c>
-      <c r="E1527" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F1527" s="8">
-        <v>5</v>
+      <c r="E1527" t="s">
+        <v>3393</v>
+      </c>
+      <c r="F1527">
+        <v>5000</v>
       </c>
     </row>
     <row r="1528" spans="1:6" ht="15.6">
@@ -41921,11 +41954,11 @@
       <c r="D1528" s="13" t="s">
         <v>1573</v>
       </c>
-      <c r="E1528" s="10" t="s">
-        <v>101</v>
+      <c r="E1528" t="s">
+        <v>3392</v>
       </c>
       <c r="F1528" s="8">
-        <v>5</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1529" spans="1:6" ht="15.6">
@@ -41941,11 +41974,11 @@
       <c r="D1529" s="13" t="s">
         <v>1574</v>
       </c>
-      <c r="E1529" s="10" t="s">
-        <v>101</v>
+      <c r="E1529" s="21" t="s">
+        <v>3391</v>
       </c>
       <c r="F1529" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1530" spans="1:6" ht="15.6">
@@ -50782,10 +50815,10 @@
         <v>2016</v>
       </c>
       <c r="E1971" t="s">
-        <v>3375</v>
+        <v>3389</v>
       </c>
       <c r="F1971">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="1972" spans="1:6" ht="15.6">
@@ -50802,7 +50835,7 @@
         <v>2017</v>
       </c>
       <c r="E1972" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="F1972" s="8">
         <v>8</v>
@@ -50822,7 +50855,7 @@
         <v>2018</v>
       </c>
       <c r="E1973" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="F1973">
         <v>24</v>
@@ -50842,7 +50875,7 @@
         <v>2019</v>
       </c>
       <c r="E1974" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="F1974" s="8">
         <v>22.5</v>
@@ -50862,7 +50895,7 @@
         <v>2020</v>
       </c>
       <c r="E1975" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="F1975" s="8">
         <v>0.04</v>
@@ -50882,7 +50915,7 @@
         <v>2021</v>
       </c>
       <c r="E1976" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="F1976">
         <v>6.25E-2</v>
@@ -50902,7 +50935,7 @@
         <v>2022</v>
       </c>
       <c r="E1977" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="F1977">
         <v>0.125</v>
@@ -50922,10 +50955,10 @@
         <v>2023</v>
       </c>
       <c r="E1978" t="s">
-        <v>3382</v>
+        <v>3390</v>
       </c>
       <c r="F1978">
-        <v>1.41</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="1979" spans="1:6" ht="15.6">
@@ -50942,7 +50975,7 @@
         <v>2024</v>
       </c>
       <c r="E1979" t="s">
-        <v>3383</v>
+        <v>3381</v>
       </c>
       <c r="F1979" s="8">
         <v>0.3</v>
@@ -50962,7 +50995,7 @@
         <v>3367</v>
       </c>
       <c r="E1980" t="s">
-        <v>3384</v>
+        <v>3382</v>
       </c>
       <c r="F1980" s="8">
         <v>540</v>
@@ -50982,7 +51015,7 @@
         <v>3368</v>
       </c>
       <c r="E1981" t="s">
-        <v>3385</v>
+        <v>3383</v>
       </c>
       <c r="F1981" s="8">
         <v>8</v>
@@ -51002,7 +51035,7 @@
         <v>3369</v>
       </c>
       <c r="E1982" t="s">
-        <v>3386</v>
+        <v>3384</v>
       </c>
       <c r="F1982">
         <v>270</v>
@@ -51022,7 +51055,7 @@
         <v>3370</v>
       </c>
       <c r="E1983" s="20" t="s">
-        <v>3387</v>
+        <v>3385</v>
       </c>
       <c r="F1983" s="8">
         <v>45</v>
@@ -51042,7 +51075,7 @@
         <v>3371</v>
       </c>
       <c r="E1984" t="s">
-        <v>3388</v>
+        <v>3386</v>
       </c>
       <c r="F1984" s="8">
         <v>8</v>
@@ -51062,7 +51095,7 @@
         <v>3372</v>
       </c>
       <c r="E1985" t="s">
-        <v>3389</v>
+        <v>3387</v>
       </c>
       <c r="F1985" s="8">
         <v>20</v>
@@ -51082,7 +51115,7 @@
         <v>3373</v>
       </c>
       <c r="E1986" t="s">
-        <v>3390</v>
+        <v>3388</v>
       </c>
       <c r="F1986" s="8">
         <v>100</v>

--- a/src/sources/exercises.xlsx
+++ b/src/sources/exercises.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Илья\Documents\physics\src\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD83079-0900-46EA-A40E-C582CAE21C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73CE45F-9F38-4845-89B2-541345A846DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8964" xr2:uid="{B3789CC9-61E8-47BE-93CC-76E693329D75}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6499" uniqueCount="3480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6499" uniqueCount="3490">
   <si>
     <r>
       <t xml:space="preserve">Множество </t>
@@ -10824,6 +10824,58 @@
   </si>
   <si>
     <t>Полная механическая энергия - это сумма кинетической и потенциальной энергии</t>
+  </si>
+  <si>
+    <t>Используйте формулу работы силы тяжести: A = Eп₁ – Eп₂, где Eп = mgh. Найдите разность потенциальной энергии на высотах h₁ и h₂</t>
+  </si>
+  <si>
+    <t>Используйте формулу кинетической энергии Eк = mv²/2, где Eк₂ = 400 Дж, m = 2 кг. Выразите v₂ (скорость на высоте h₂) и вычислите её</t>
+  </si>
+  <si>
+    <t>Используйте формулу внутренней энергии идеального газа: U = E₀ · N, где U — внутренняя энергия, E₀ — средняя кинетическая энергия одной молекулы, N — количество молекул. Выразите E₀ и подставьте известные значения</t>
+  </si>
+  <si>
+    <t>Найдите разницу между конечной и начальной внутренней энергией: ΔU = U₁ – U₀. Используйте прирост энергии одной молекулы (4 Дж) и количество молекул (N = 20)</t>
+  </si>
+  <si>
+    <r>
+      <t>Используйте формулу первого закона термодинамики: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="YS Geo"/>
+      </rPr>
+      <t>Q = ΔU + A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Найдите ΔU как разницу между U₂ и U₁, затем прибавьте к ней работу A (20 Дж)</t>
+    </r>
+  </si>
+  <si>
+    <t>Найдите Q как сумму начальных кинетических энергий шаров (1000 Дж + 1000 Дж). Затем используйте формулу Q = N·(Eм₁ – Eм₀), чтобы найти разницу Eм₁ – Eм₀. N = 1000 молекул</t>
+  </si>
+  <si>
+    <t>Найдите общую начальную кинетическую энергию (2 × 2000 Дж), умножьте на 0,7 (70% на нагрев), получите Q. Затем используйте формулу ΔU = N · (Eм₁ – Eм₀), чтобы найти Eм₁ – Eм₀. N = 100 молекул</t>
+  </si>
+  <si>
+    <t>Найдите Eп₁ (потенциальная энергия на h₁) и Eп₄ (на h₄) по формуле mgh. Разница между ними — это Q (потерянная энергия, перешедшая в тепло). Используйте g = 10 м/с²</t>
+  </si>
+  <si>
+    <t>Вычтите Eп₄ из Eп₁ — получите Q. Умножьте Q на 0,6 — это и будет ΔU (изменение внутренней энергии). Используйте g = 9,8 м/с²</t>
+  </si>
+  <si>
+    <t>Рассчитайте Eп₁ (на h₁) и Eп₄ (на h₄) по mgh. Найдите Q = Eп₁ – Eп₄. Вычислите Qт = Q · 0,6 (изменение внутр. энергии). Разделите Qт на N (число молекул) — получите ΔEм</t>
   </si>
 </sst>
 </file>
@@ -45704,11 +45756,11 @@
       <c r="D1691" s="13" t="s">
         <v>1715</v>
       </c>
-      <c r="E1691" s="10" t="s">
-        <v>101</v>
+      <c r="E1691" t="s">
+        <v>3480</v>
       </c>
       <c r="F1691" s="8">
-        <v>5</v>
+        <v>300</v>
       </c>
     </row>
     <row r="1692" spans="1:6" ht="15.6">
@@ -45724,11 +45776,11 @@
       <c r="D1692" s="13" t="s">
         <v>1716</v>
       </c>
-      <c r="E1692" s="10" t="s">
-        <v>101</v>
+      <c r="E1692" t="s">
+        <v>3481</v>
       </c>
       <c r="F1692" s="8">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1693" spans="1:6" ht="15.6">
@@ -45744,8 +45796,8 @@
       <c r="D1693" s="13" t="s">
         <v>1717</v>
       </c>
-      <c r="E1693" s="10" t="s">
-        <v>101</v>
+      <c r="E1693" t="s">
+        <v>3482</v>
       </c>
       <c r="F1693" s="8">
         <v>5</v>
@@ -45764,11 +45816,11 @@
       <c r="D1694" s="13" t="s">
         <v>1718</v>
       </c>
-      <c r="E1694" s="10" t="s">
-        <v>101</v>
+      <c r="E1694" t="s">
+        <v>3483</v>
       </c>
       <c r="F1694" s="8">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1695" spans="1:6" ht="15.6">
@@ -45784,11 +45836,11 @@
       <c r="D1695" s="13" t="s">
         <v>1719</v>
       </c>
-      <c r="E1695" s="10" t="s">
-        <v>101</v>
+      <c r="E1695" t="s">
+        <v>3484</v>
       </c>
       <c r="F1695" s="8">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1696" spans="1:6" ht="15.6">
@@ -45804,11 +45856,11 @@
       <c r="D1696" s="13" t="s">
         <v>1720</v>
       </c>
-      <c r="E1696" s="10" t="s">
-        <v>101</v>
+      <c r="E1696" t="s">
+        <v>3485</v>
       </c>
       <c r="F1696" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1697" spans="1:6" ht="15.6">
@@ -45824,11 +45876,11 @@
       <c r="D1697" s="13" t="s">
         <v>1721</v>
       </c>
-      <c r="E1697" s="10" t="s">
-        <v>101</v>
+      <c r="E1697" t="s">
+        <v>3486</v>
       </c>
       <c r="F1697" s="8">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1698" spans="1:6" ht="15.6">
@@ -45844,11 +45896,11 @@
       <c r="D1698" s="13" t="s">
         <v>1722</v>
       </c>
-      <c r="E1698" s="10" t="s">
-        <v>101</v>
+      <c r="E1698" t="s">
+        <v>3487</v>
       </c>
       <c r="F1698" s="8">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1699" spans="1:6" ht="15.6">
@@ -45864,11 +45916,11 @@
       <c r="D1699" s="13" t="s">
         <v>1723</v>
       </c>
-      <c r="E1699" s="10" t="s">
-        <v>101</v>
+      <c r="E1699" t="s">
+        <v>3488</v>
       </c>
       <c r="F1699" s="8">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1700" spans="1:6" ht="15.6">
@@ -45884,11 +45936,11 @@
       <c r="D1700" s="13" t="s">
         <v>1724</v>
       </c>
-      <c r="E1700" s="10" t="s">
-        <v>101</v>
+      <c r="E1700" t="s">
+        <v>3489</v>
       </c>
       <c r="F1700" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1701" spans="1:6" ht="15.6">
